--- a/code/output/dat.social.type.token.sequential.xlsx
+++ b/code/output/dat.social.type.token.sequential.xlsx
@@ -172,7 +172,7 @@
     <t>testable</t>
   </si>
   <si>
-    <t>city</t>
+    <t>students</t>
   </si>
   <si>
     <t>159771_230816_114022_b090d65b2011227cef032f263c8e46ff2aec1c38.csv</t>
